--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -3375,7 +3375,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5186,34 +5186,34 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>32041500</v>
+        <v>30119000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>24609</v>
+        <v>23133</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>30119010</v>
+        <v>30119000</v>
       </c>
       <c r="L68" s="5" t="n">
         <v>23133</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J180" s="3" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="N180" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20205,7 +20205,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23490,7 +23490,7 @@
           <t>B | 1276呎 (3房)
 $3228万
 $25,300/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -23578,7 +23578,7 @@
           <t>A | 1625呎 (4+房)
 $5165万
 $31,782/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -23610,7 +23610,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -23642,7 +23642,7 @@
           <t>A | 1625呎 (4+房)
 $4962万
 $30,535/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -23650,7 +23650,7 @@
           <t>B | 1226呎 (3房)
 $2789万
 $22,745/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -23658,7 +23658,7 @@
           <t>C | 1304呎 (3房)
 $2875万
 $22,050/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -23674,7 +23674,7 @@
           <t>A | 1625呎 (4+房)
 $4791万
 $29,482/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -23706,7 +23706,7 @@
           <t>A | 1711呎 (4+房)
 $4600万
 $26,885/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -23714,7 +23714,7 @@
           <t>B | 1226呎 (3房)
 $3061万
 $24,969/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -23722,7 +23722,7 @@
           <t>C | 1254呎 (3房)
 $2960万
 $23,605/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -23738,7 +23738,7 @@
           <t>A | 945呎 (3房)
 $2145万
 $22,700/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -23746,7 +23746,7 @@
           <t>B | 1226呎 (3房)
 $3015万
 $24,594/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -23754,7 +23754,7 @@
           <t>C | 1252呎 (3房)
 $2591万
 $20,695/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -23762,7 +23762,7 @@
           <t>D | 724呎 (2房)
 $1643万
 $22,700/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
           <t>A | 945呎 (3房)
 $2060万
 $21,800/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -23785,15 +23785,15 @@
           <t>B | 1226呎 (3房)
 $2942万
 $24,000/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 1302呎 (3房)
-$3204万
-$24,609/呎
-(在售)</t>
+$3012万
+$23,133/呎
+(26年-07月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -23801,7 +23801,7 @@
           <t>D | 724呎 (2房)
 $1578万
 $21,800/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -23816,7 +23816,7 @@
           <t>A | 945呎 (3房)
 $1975万
 $20,900/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -23824,7 +23824,7 @@
           <t>B | 1226呎 (3房)
 $2897万
 $23,626/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -23832,7 +23832,7 @@
           <t>C | 1302呎 (3房)
 $2966万
 $22,780/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -23840,7 +23840,7 @@
           <t>D | 724呎 (2房)
 $1513万
 $20,900/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -23855,7 +23855,7 @@
           <t>A | 945呎 (3房)
 $1909万
 $20,200/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -23863,7 +23863,7 @@
           <t>B | 1226呎 (3房)
 $2475万
 $20,191/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>C | 1252呎 (3房)
 $2708万
 $21,631/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>D | 724呎 (2房)
 $1548万
 $21,380/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
           <t>A | 945呎 (3房)
 $1843万
 $19,500/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -23902,7 +23902,7 @@
           <t>B | 1226呎 (3房)
 $2419万
 $19,733/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -23910,7 +23910,7 @@
           <t>C | 1252呎 (3房)
 $2331万
 $18,615/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -23918,7 +23918,7 @@
           <t>D | 724呎 (2房)
 $1419万
 $19,600/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -23933,7 +23933,7 @@
           <t>A | 945呎 (3房)
 $1777万
 $18,800/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -23941,7 +23941,7 @@
           <t>B | 1226呎 (3房)
 $2348万
 $19,150/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -23949,7 +23949,7 @@
           <t>C | 1252呎 (3房)
 $2292万
 $18,303/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -23957,7 +23957,7 @@
           <t>D | 724呎 (2房)
 $1361万
 $18,800/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -23972,7 +23972,7 @@
           <t>A | 945呎 (3房)
 $1692万
 $17,900/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -23980,7 +23980,7 @@
           <t>B | 1226呎 (3房)
 $2549万
 $20,789/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -23988,7 +23988,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -23996,7 +23996,7 @@
           <t>D | 724呎 (2房)
 $1300万
 $17,950/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -24011,7 +24011,7 @@
           <t>A | 945呎 (3房)
 $1635万
 $17,300/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -24019,7 +24019,7 @@
           <t>B | 1226呎 (3房)
 $2463万
 $20,087/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -24027,7 +24027,7 @@
           <t>C | 1252呎 (3房)
 $2213万
 $17,679/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -24035,7 +24035,7 @@
           <t>D | 724呎 (2房)
 $1281万
 $17,700/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -24050,7 +24050,7 @@
           <t>A | 945呎 (3房)
 $1577万
 $16,688/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -24058,7 +24058,7 @@
           <t>B | 1226呎 (3房)
 $2450万
 $19,983/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -24066,7 +24066,7 @@
           <t>C | 1252呎 (3房)
 $2252万
 $17,991/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -24074,7 +24074,7 @@
           <t>D | 724呎 (2房)
 $1339万
 $18,499/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -24089,7 +24089,7 @@
           <t>A | 1532呎 (4+房)
 $3964万
 $25,873/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -24097,7 +24097,7 @@
           <t>B | 1210呎 (3房)
 $2884万
 $23,836/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -24105,7 +24105,7 @@
           <t>C | 1254呎 (3房)
 $2478万
 $19,758/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -25002,7 +25002,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -25171,12 +25171,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1865呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -25202,7 +25202,7 @@
           <t>F | 769呎 (3房)
 $1821万
 $23,684/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
           <t>A | 1788呎 (4+房)
 $6600万
 $36,913/呎
-(26年-06月-29日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25243,7 +25243,7 @@
           <t>F | 769呎 (3房)
 $1803万
 $23,450/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
           <t>A | 1788呎 (4+房)
 $6900万
 $38,593/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -25284,7 +25284,7 @@
           <t>F | 769呎 (3房)
 $1785万
 $23,217/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -25299,7 +25299,7 @@
           <t>A | 1788呎 (4+房)
 $5908万
 $33,044/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -25325,7 +25325,7 @@
           <t>F | 769呎 (3房)
 $1682万
 $21,872/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -25340,7 +25340,7 @@
           <t>A | 1788呎 (4+房)
 $6051万
 $33,841/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -25366,7 +25366,7 @@
           <t>F | 769呎 (3房)
 $1628万
 $21,172/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
           <t>A | 1788呎 (4+房)
 $5456万
 $30,514/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -25407,7 +25407,7 @@
           <t>F | 769呎 (3房)
 $1574万
 $20,473/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -25422,7 +25422,7 @@
           <t>A | 985呎 (3房)
 $2289万
 $23,239/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25430,7 +25430,7 @@
           <t>B | 725呎 (2房)
 $1579万
 $21,775/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25438,7 +25438,7 @@
           <t>C | 961呎 (3房)
 $2704万
 $28,133/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -25462,7 +25462,7 @@
           <t>F | 769呎 (3房)
 $1528万
 $19,874/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -25477,7 +25477,7 @@
           <t>A | 985呎 (3房)
 $2090万
 $21,216/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25485,7 +25485,7 @@
           <t>B | 725呎 (2房)
 $1548万
 $21,348/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -25517,7 +25517,7 @@
           <t>F | 769呎 (3房)
 $1490万
 $19,375/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25532,7 @@
           <t>A | 985呎 (3房)
 $2009万
 $20,400/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25540,7 +25540,7 @@
           <t>B | 725呎 (2房)
 $1517万
 $20,929/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -25572,7 +25572,7 @@
           <t>F | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -25587,7 +25587,7 @@
           <t>A | 985呎 (3房)
 $1931万
 $19,600/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25595,7 +25595,7 @@
           <t>B | 725呎 (2房)
 $1467万
 $20,228/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -25627,7 +25627,7 @@
           <t>F | 769呎 (3房)
 $1448万
 $18,828/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25642,7 @@
           <t>A | 985呎 (3房)
 $1862万
 $18,900/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25650,7 +25650,7 @@
           <t>B | 727呎 (2房)
 $1423万
 $19,573/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -25669,7 +25669,7 @@
           <t>A | 985呎 (3房)
 $1807万
 $18,350/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25677,7 +25677,7 @@
           <t>B | 729呎 (2房)
 $1383万
 $18,974/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -25696,7 +25696,7 @@
           <t>A | 985呎 (3房)
 $1753万
 $17,800/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25704,7 +25704,7 @@
           <t>B | 729呎 (2房)
 $1416万
 $19,417/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr"/>
@@ -25723,7 +25723,7 @@
           <t>A | 985呎 (3房)
 $1714万
 $17,400/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25731,7 +25731,7 @@
           <t>B | 729呎 (2房)
 $1281万
 $17,576/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>
@@ -25750,7 +25750,7 @@
           <t>A | 985呎 (3房)
 $1684万
 $17,100/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -25758,7 +25758,7 @@
           <t>B | 729呎 (2房)
 $1252万
 $17,176/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr"/>
@@ -25777,7 +25777,7 @@
           <t>A | 1640呎 (3房)
 $4380万
 $26,707/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr"/>
@@ -25936,7 +25936,7 @@
           <t>C | 769呎 (3房)
 $1586万
 $20,623/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -25944,7 +25944,7 @@
           <t>D | 712呎 (2房)
 $1504万
 $21,126/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -25975,7 +25975,7 @@
           <t>C | 769呎 (3房)
 $1563万
 $20,324/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -25983,7 +25983,7 @@
           <t>D | 712呎 (2房)
 $1478万
 $20,758/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -26014,7 +26014,7 @@
           <t>C | 769呎 (3房)
 $1540万
 $20,024/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>D | 712呎 (2房)
 $1452万
 $20,390/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
           <t>C | 769呎 (3房)
 $1517万
 $19,724/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26061,7 +26061,7 @@
           <t>D | 712呎 (2房)
 $1356万
 $19,050/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -26092,7 +26092,7 @@
           <t>C | 769呎 (3房)
 $1494万
 $19,425/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26100,7 +26100,7 @@
           <t>D | 712呎 (2房)
 $1339万
 $18,800/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
           <t>A | 1498呎 (4+房)
 $3810万
 $25,432/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -26131,7 +26131,7 @@
           <t>C | 769呎 (3房)
 $1471万
 $19,125/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26139,7 +26139,7 @@
           <t>D | 712呎 (2房)
 $1321万
 $18,550/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -26170,7 +26170,7 @@
           <t>C | 769呎 (3房)
 $1452万
 $18,875/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26178,7 +26178,7 @@
           <t>D | 712呎 (2房)
 $1296万
 $18,200/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -26209,7 +26209,7 @@
           <t>C | 769呎 (3房)
 $1432万
 $18,626/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26217,7 +26217,7 @@
           <t>D | 712呎 (2房)
 $1278万
 $17,950/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -26232,7 +26232,7 @@
           <t>A | 1555呎 (4+房)
 $3703万
 $23,814/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -26248,7 +26248,7 @@
           <t>C | 769呎 (3房)
 $1398万
 $18,176/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -26256,7 +26256,7 @@
           <t>D | 712呎 (2房)
 $1257万
 $17,650/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26271,7 +26271,7 @@
           <t>A | 1498呎 (4+房)
 $3370万
 $22,497/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -26287,7 +26287,7 @@
           <t>C | 769呎 (3房)
 $1379万
 $17,927/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26295,7 +26295,7 @@
           <t>D | 712呎 (2房)
 $1242万
 $17,450/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
           <t>A | 1498呎 (4+房)
 $3314万
 $22,121/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -26326,7 +26326,7 @@
           <t>C | 768呎 (3房)
 $1432万
 $18,642/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>D | 712呎 (2房)
 $1228万
 $17,250/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -26349,7 +26349,7 @@
           <t>A | 1498呎 (4+房)
 $3234万
 $21,591/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26357,7 +26357,7 @@
           <t>B | 1473呎 (4+房)
 $3244万
 $22,020/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>C | 769呎 (3房)
 $1340万
 $17,427/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>D | 712呎 (2房)
 $1214万
 $17,050/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -26388,7 +26388,7 @@
           <t>A | 1498呎 (4+房)
 $3380万
 $22,562/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26396,7 +26396,7 @@
           <t>B | 1473呎 (4+房)
 $3583万
 $24,327/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26404,7 +26404,7 @@
           <t>C | 769呎 (3房)
 $1321万
 $17,178/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26412,7 +26412,7 @@
           <t>D | 712呎 (2房)
 $1200万
 $16,850/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
           <t>A | 1498呎 (4+房)
 $3140万
 $20,960/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -26443,7 +26443,7 @@
           <t>C | 769呎 (3房)
 $1297万
 $16,866/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26451,7 +26451,7 @@
           <t>D | 712呎 (2房)
 $1139万
 $15,998/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
     </row>
@@ -26466,7 +26466,7 @@
           <t>A | 1498呎 (4+房)
 $3079万
 $20,553/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26474,7 +26474,7 @@
           <t>B | 1478呎 (4+房)
 $3343万
 $22,621/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr"/>
@@ -26491,7 +26491,7 @@
           <t>A | 1498呎 (4+房)
 $3110万
 $20,761/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26499,7 +26499,7 @@
           <t>B | 1478呎 (4+房)
 $2993万
 $20,252/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr"/>
@@ -26516,7 +26516,7 @@
           <t>A | 1498呎 (4+房)
 $3063万
 $20,450/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -26541,7 +26541,7 @@
           <t>A | 1498呎 (4+房)
 $3126万
 $20,865/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26549,7 +26549,7 @@
           <t>B | 1488呎 (4+房)
 $2930万
 $19,691/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr"/>

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -12722,7 +12722,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -24982,12 +24982,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -25171,12 +25171,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 1865呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -26710,34 +26710,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23463,29 +23463,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23493,7 +23475,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23501,6 +23483,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24261,44 +24261,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25073,41 +25073,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25115,7 +25088,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25123,6 +25096,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26710,34 +26710,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1302</v>
+        <v>1252</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>30119000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>23133</v>
+        <v>24057</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>30119000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>23133</v>
+        <v>24057</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1302</v>
+        <v>1252</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
         <v>29659560</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>22780</v>
+        <v>23690</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>29659560</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>22780</v>
+        <v>23690</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -12722,38 +12722,30 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>66880000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>35861</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K180" s="5" t="n">
+        <v>66880000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>35861</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -12762,7 +12754,7 @@
       </c>
       <c r="N180" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23463,11 +23455,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23475,7 +23485,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23483,24 +23493,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23790,9 +23782,9 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>C | 1302呎 (3房)
+          <t>C | 1252呎 (3房)
 $3012万
-$23,133/呎
+$24,057/呎
 (26年-07月-26日)</t>
         </is>
       </c>
@@ -23829,10 +23821,10 @@
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>C | 1302呎 (3房)
+          <t>C | 1252呎 (3房)
 $2966万
-$22,780/呎
-(26年-07月-21日)</t>
+$23,690/呎
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -24261,44 +24253,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24982,7 +24974,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24992,7 +24984,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25073,14 +25065,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25088,7 +25107,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25097,33 +25116,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25171,12 +25163,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1865呎 (4+房)
-招标单位
--
-(在售)</t>
+$6688万
+$35,861/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23455,29 +23455,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23485,7 +23467,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23493,6 +23475,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24253,44 +24253,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25065,41 +25065,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25107,7 +25080,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25115,6 +25088,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26702,34 +26702,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23455,11 +23455,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23467,7 +23485,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23475,24 +23493,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24253,44 +24253,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25065,14 +25065,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25080,7 +25107,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25088,33 +25115,6 @@
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26702,34 +26702,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23376,27 +23376,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -23677,12 +23677,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -26702,34 +26702,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -4496,38 +4496,30 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>32339200</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>24800</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K57" s="5" t="n">
+        <v>32339200</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>24800</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4536,7 +4528,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12718,7 +12710,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1865</v>
+        <v>1788</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -12727,14 +12719,14 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
         <v>66880000</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>35861</v>
+        <v>37405</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -12745,7 +12737,7 @@
         <v>66880000</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>35861</v>
+        <v>37405</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -13708,34 +13700,34 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>58826600</v>
+        <v>55297000</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>31695</v>
+        <v>29794</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>55297004</v>
+        <v>55297000</v>
       </c>
       <c r="L195" s="5" t="n">
         <v>29794</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -23376,7 +23368,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23386,7 +23378,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23455,11 +23447,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23467,7 +23477,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23475,24 +23485,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23677,12 +23669,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
-招标单位
--
-(在售)</t>
+$3234万
+$24,800/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -24253,44 +24245,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24979,12 +24971,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25065,14 +25057,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25080,7 +25099,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25089,33 +25108,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25165,10 +25157,10 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1865呎 (4+房)
+          <t>A | 1788呎 (4+房)
 $6688万
-$35,861/呎
-(26年-08月-03日)</t>
+$37,405/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -25335,12 +25327,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1856呎 (4+房)
-$5883万
-$31,695/呎
-(已定价未售)</t>
+$5530万
+$29,794/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr"/>
@@ -26702,34 +26694,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -23777,7 +23777,7 @@
           <t>C | 1252呎 (3房)
 $3012万
 $24,057/呎
-(26年-07月-26日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26694,34 +26694,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -131,13 +131,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23368,27 +23368,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -23447,29 +23447,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23477,7 +23459,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23485,6 +23467,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23493,12 +23493,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1711呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -23533,7 +23533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3831万
@@ -23541,7 +23541,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 $3690万
@@ -23661,7 +23661,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3549万
@@ -24245,44 +24245,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25045,7 +25045,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1996万
@@ -25057,41 +25057,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25099,7 +25072,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25108,6 +25081,33 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1957万
@@ -25368,7 +25368,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1856呎 (4+房)
 $5603万
@@ -25472,7 +25472,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2820万
@@ -25527,7 +25527,7 @@
 (26年-06月-09日)</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2764万
@@ -25582,7 +25582,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2690万
@@ -25938,7 +25938,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
 $4811万
@@ -25946,7 +25946,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4733万
@@ -25977,7 +25977,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
 $4679万
@@ -25985,7 +25985,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4635万
@@ -26024,7 +26024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4536万
@@ -26219,7 +26219,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4101万
@@ -26258,7 +26258,7 @@
 (26年-01月-06日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4080万
@@ -26297,7 +26297,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4021万
@@ -26414,7 +26414,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $3766万
@@ -26694,34 +26694,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23447,11 +23447,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23459,7 +23477,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23467,24 +23485,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24245,44 +24245,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25057,14 +25057,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25072,7 +25099,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25080,33 +25107,6 @@
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26694,34 +26694,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23447,29 +23447,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23477,7 +23459,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23485,6 +23467,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24245,44 +24245,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25057,41 +25057,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25099,7 +25072,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25107,6 +25080,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26694,34 +26694,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -131,13 +131,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3642,38 +3642,30 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>62964800</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>36800</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K44" s="5" t="n">
+        <v>62964800</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>36800</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3682,7 +3674,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23368,7 +23360,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23378,7 +23370,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23447,11 +23439,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23459,7 +23469,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23467,24 +23477,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23493,12 +23485,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1711呎 (4+房)
-招标单位
--
-(在售)</t>
+$6296万
+$36,800/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -23533,7 +23525,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3831万
@@ -23541,7 +23533,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 $3690万
@@ -23661,7 +23653,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3549万
@@ -24245,44 +24237,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25045,7 +25037,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1996万
@@ -25057,14 +25049,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25072,7 +25091,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25081,33 +25100,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25140,7 +25132,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1957万
@@ -25368,7 +25360,7 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1856呎 (4+房)
 $5603万
@@ -25472,7 +25464,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2820万
@@ -25527,7 +25519,7 @@
 (26年-06月-09日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2764万
@@ -25582,7 +25574,7 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
 $2690万
@@ -25938,7 +25930,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
 $4811万
@@ -25946,7 +25938,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4733万
@@ -25977,7 +25969,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
 $4679万
@@ -25985,7 +25977,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4635万
@@ -26024,7 +26016,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4536万
@@ -26219,7 +26211,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4101万
@@ -26258,7 +26250,7 @@
 (26年-01月-06日)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4080万
@@ -26297,7 +26289,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $4021万
@@ -26414,7 +26406,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
 $3766万
@@ -26694,34 +26686,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
